--- a/sql/script/data/rss_list.xlsx
+++ b/sql/script/data/rss_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT_PYTHON\sea_platform\sql\script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726CE494-EE6C-4B21-BAD6-BA30DB5E562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A8E379-B684-40B2-B4B8-258C16997DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="204">
   <si>
     <t>id</t>
   </si>
@@ -55,434 +55,591 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>国内焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=civilnews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>台湾焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=taiwan&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>港澳焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=gangaotai&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>国际焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=internews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>环球视野焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=hqsy&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>国际人物焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=renwu&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>军事焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=mil&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>中国军情焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=zhongguojq&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>台海聚焦焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=taihaijj&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>国际军情焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=guojijq&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>财经焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=finannews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>股票焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=stock&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>理财焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=money&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>宏观经济焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=hongguan&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>产业经济焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=chanye&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>互联网焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=internet&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>人物动态焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=rwdt&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>公司动态焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=gsdt&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>搜索引擎焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=search_engine&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>电子商务焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=e_commerce&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>网络游戏焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=online_game&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>房产焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=housenews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>各地动态焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=gddt&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>政策风向焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=zcfx&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>市场走势焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=shichangzoushi&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>家居焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=fitment&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>汽车焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=autonews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>新车焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=autobuy&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>导购焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=daogou&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>各地行情焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=hangqing&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>维修养护焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=weixiu&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>体育焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=sportnews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>NBA焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=nba&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>国际足球焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=worldsoccer&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>国内足球焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=chinasoccer&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>CBA焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=cba&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>综合体育焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=othersports&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>娱乐焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=enternews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>明星焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=star&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>电影焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=film&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>电视焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=tv&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>音乐焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=music&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>综艺焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=zongyi&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>演出焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=yanchu&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>奖项焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=jiangxiang&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>游戏焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=gamenews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=netgames&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>电视游戏焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=tvgames&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>电子竞技焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=dianzijingji&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>热门游戏焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=remenyouxi&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>魔兽世界焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=WOW&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>教育焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=edunews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>考试焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=exams&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>留学焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=abroad&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>就业焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=jiuye&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>女人焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=healthnews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>潮流服饰焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=chaoliufs&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>美容护肤焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=meironghf&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>减肥健身焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=jianfei&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>情感两性焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=qinggan&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>健康养生焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=jiankang&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>科技焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=technnews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>手机焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=cell&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>数码焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=digital&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>电脑焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=computer&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>科普焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=discovery&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>社会焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=socianews&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>社会与法焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=shyf&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>社会万象焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=shwx&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>真情时刻焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=zqsk&amp;tn=rss</t>
-  </si>
-  <si>
-    <t>奇闻异事焦点（百度源）</t>
-  </si>
-  <si>
-    <t>http://news.baidu.com/n?cmd=1&amp;class=qwys&amp;tn=rss</t>
+    <t>国内最新（百度源）</t>
+  </si>
+  <si>
+    <t>时政要闻最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=shizheng&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>高层动态最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=gaoceng&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>人事任免最新（百度源）</t>
+  </si>
+  <si>
+    <t>台湾最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=taiwan&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>历史档案最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=lishi&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>台湾民生最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=twms&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>港澳最新（百度源）</t>
+  </si>
+  <si>
+    <t>国际最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=internews&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>环球视野最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=hqsy&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>国际人物最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=renwu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>军事最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=mil&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>中国军情最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=zhongguojq&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>台海聚焦最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=taihaijj&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>国际军情最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=guojijq&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>财经最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=finannews&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>股票最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=stock&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>大盘最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=dapan&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>个股最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=gegu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>新股最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=xingu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>权证最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=warrant&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>理财最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=money&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>基金最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=fund&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>银行最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=bank&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>贵金属最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=nmetal&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>保险最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=insurance&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>外汇最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=forex&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>期货最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=futures&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>宏观经济最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=hongguan&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=hg_guonei&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=hg_guoji&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>产业经济最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=chanye&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>互联网最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=internet&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>人物动态最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=rwdt&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>公司动态最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=gsdt&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>搜索引擎最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=search_engine&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>电子商务最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=e_commerce&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>网络游戏最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=online_game&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>房产最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=housenews&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>各地动态最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=gddt&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>政策风向最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=zcfx&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>市场走势最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=shichangzoushi&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>家居最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=fitment&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>汽车最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=autonews&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>新车最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=autobuy&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>导购最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=daogou&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>各地行情最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=hangqing&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>维修养护最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=weixiu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>体育最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=sportnews&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>NBA最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=nba&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>姚明-火箭最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=yaoming&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>易建联-篮网最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=yijianlian&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>国际足球最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=worldsoccer&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>英超最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Yingchao&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>意甲最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Yijia&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>西甲最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Xijia&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>足球明星最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Zq_star&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>曼联最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Manutd&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>阿森纳最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Arsenal&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>切尔西最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Chelsea&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>利物浦最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Liverpool&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>AC米兰最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=ACMilan&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>国际米兰最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=InterMilan&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>尤文图斯最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Juventus&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>皇马最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=RealMadrid&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>巴塞罗那最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Barcelona&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>拜仁最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Bayen&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>国内足球最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=chinasoccer&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>男足最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=nanzu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>女足最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=nvzu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>中超最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=zhongchao&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>球迷最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=cn_qiumi&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>CBA最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=cba&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>赛事最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=cba_match&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>综合体育最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=othersports&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>排球最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=volleyball&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>乒乓球最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=table-tennis&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>羽毛球最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=badminton&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>田径最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Athletics&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>游泳最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=swimming&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>体操最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=Gymnastics&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>网球最新（百度源）</t>
+  </si>
+  <si>
+    <t>赛车最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=F1&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>拳击最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=boxing&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>台球最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=billiards&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>娱乐最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=enternews&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>明星最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=star&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>爆料最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=star_chuanwen&amp;pn=1</t>
+  </si>
+  <si>
+    <t>港台最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=star_gangtai&amp;pn=1</t>
+  </si>
+  <si>
+    <t>内地最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=star_neidi&amp;pn=1</t>
+  </si>
+  <si>
+    <t>欧美最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=star_oumei&amp;pn=1</t>
+  </si>
+  <si>
+    <t>日韩最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=star_rihan&amp;pn=1</t>
+  </si>
+  <si>
+    <t>电影最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=film&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>电影花絮最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=film_huaxu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>电视最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=tv&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>剧评最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=tv_jupin&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>音乐最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=music&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>综艺最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=zongyi&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>演出最新（百度源）</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=yanchu&amp;tn=rss</t>
+  </si>
+  <si>
+    <t>http://news.baidu.com/n?cmd=4&amp;class=civilnews&amp;tn=rss</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,6 +658,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -536,17 +701,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -846,8 +1014,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -886,710 +1057,710 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
+      <c r="C2" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>20</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="H27">
         <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
+        <v>105</v>
+      </c>
+      <c r="B35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="H35">
         <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -1600,268 +1771,268 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="H48">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="H49">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="H55">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -1872,227 +2043,706 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="H60">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C68" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="B70" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C70" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="B72" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" t="s">
+        <v>147</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>143</v>
+      </c>
+      <c r="B73" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" t="s">
+        <v>149</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>144</v>
+      </c>
+      <c r="B74" t="s">
         <v>150</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C74" t="s">
         <v>151</v>
       </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <v>25</v>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" t="s">
+        <v>153</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>146</v>
+      </c>
+      <c r="B76" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" t="s">
+        <v>155</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>147</v>
+      </c>
+      <c r="B77" t="s">
+        <v>156</v>
+      </c>
+      <c r="C77" t="s">
+        <v>157</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>149</v>
+      </c>
+      <c r="B79" t="s">
+        <v>160</v>
+      </c>
+      <c r="C79" t="s">
+        <v>161</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>162</v>
+      </c>
+      <c r="C80" t="s">
+        <v>163</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>151</v>
+      </c>
+      <c r="B81" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" t="s">
+        <v>165</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>152</v>
+      </c>
+      <c r="B82" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" t="s">
+        <v>167</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>153</v>
+      </c>
+      <c r="B83" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" t="s">
+        <v>157</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>154</v>
+      </c>
+      <c r="B84" t="s">
+        <v>169</v>
+      </c>
+      <c r="C84" t="s">
+        <v>170</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>155</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" t="s">
+        <v>172</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>156</v>
+      </c>
+      <c r="B86" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" t="s">
+        <v>174</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>157</v>
+      </c>
+      <c r="B87" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87" t="s">
+        <v>176</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>158</v>
+      </c>
+      <c r="B88" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88" t="s">
+        <v>178</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>159</v>
+      </c>
+      <c r="B89" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" t="s">
+        <v>180</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>160</v>
+      </c>
+      <c r="B90" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" t="s">
+        <v>182</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>161</v>
+      </c>
+      <c r="B91" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>184</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>162</v>
+      </c>
+      <c r="B92" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" t="s">
+        <v>186</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>163</v>
+      </c>
+      <c r="B93" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" t="s">
+        <v>188</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>164</v>
+      </c>
+      <c r="B94" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" t="s">
+        <v>190</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>165</v>
+      </c>
+      <c r="B95" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" t="s">
+        <v>192</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>166</v>
+      </c>
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" t="s">
+        <v>194</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>167</v>
+      </c>
+      <c r="B97" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" t="s">
+        <v>196</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>168</v>
+      </c>
+      <c r="B98" t="s">
+        <v>197</v>
+      </c>
+      <c r="C98" t="s">
+        <v>198</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>169</v>
+      </c>
+      <c r="B99" t="s">
+        <v>199</v>
+      </c>
+      <c r="C99" t="s">
+        <v>200</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>170</v>
+      </c>
+      <c r="B100" t="s">
+        <v>201</v>
+      </c>
+      <c r="C100" t="s">
+        <v>202</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2F1D4E79-1886-4D22-8129-979591F9AB8E}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>